--- a/contracts/ChainSwap/output_debug/emitting_events.xlsx
+++ b/contracts/ChainSwap/output_debug/emitting_events.xlsx
@@ -436,17 +436,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>event_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>blockID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>signature</t>
         </is>
       </c>
     </row>
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0x882df69720ac5a9356b84d2aaa32d0c105b24cab60e885ba3d69b77090ff05c6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Send(address,uint256,address,uint256,uint256)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>0x840</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0x882df69720ac5a9356b84d2aaa32d0c105b24cab60e885ba3d69b77090ff05c6</t>
         </is>
       </c>
     </row>
